--- a/光伏配储项目/电价数据/2026/孟槐站.xlsx
+++ b/光伏配储项目/电价数据/2026/孟槐站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50992</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.5332899999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54386</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45546</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44022</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44515</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25243</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.01231</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.11478</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.03079</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.02285</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03628</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08237</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00526</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14429</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21151</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23893</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15084</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01394</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11865</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.01219</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.25321</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.0799</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.17994</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.07343999999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.24107</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.5598500000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.60224</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42083</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15394</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6926100000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79431</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53661</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52301</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50637</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.46497</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42262</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51385</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6239</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72519</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.13066</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.16596</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12377</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.25725</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.14815</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.12644</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.16309</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00027</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.05983</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.11545</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.14347</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.25533</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>-0.00197</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.04225</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.03199</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.01282</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22573</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.78038</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7659199999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78674</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.13475</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.60017</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33311</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5164500000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21096</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.01355</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24853</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.13796</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.09209999999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.23058</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.16914</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.20189</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.15652</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.00463</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.08565</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.05623</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.19347</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.26763</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.18447</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.00448</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.07809999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.20651</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.22734</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.21342</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.05601</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.14203</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.09148000000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.10144</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.24139</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.22415</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34321</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.09745999999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.24938</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.05385</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03524</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.009650000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23408</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.07307999999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.00383</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.03861</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.02287</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.02885</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.03012</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.16915</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29584</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.02475</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.03925</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.01932</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04465</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04842</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14821</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.00082</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.14695</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.18588</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.21016</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.11572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.21768</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3489</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.01348</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04218</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04465</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10103</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00268</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04584000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04839</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07081999999999999</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.17715</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.23634</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.25467</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.21607</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.19256</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.21154</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.2218</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.19548</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.21678</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.19626</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.24285</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.25834</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33051</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31865</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.27853</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.25841</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.10212</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.24675</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.25968</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.24566</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.08065</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.05909</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16012</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.17535</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.11951</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.27626</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>-0.04244</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.25634</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.01454</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.11925</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.07243000000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>-0.00337</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.14971</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.10788</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-0.00231</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.05273</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.10771</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.17741</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-0.04585</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.16645</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.07740000000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.20467</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7396200000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.48966</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.23498</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.5753400000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.52018</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.2074</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.48867</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0.93444</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.48917</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.68931</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.47425</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.98093</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.6997899999999999</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7900199999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77676</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87854</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8733500000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49223</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39911</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20623</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87936</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63895</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49862</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45901</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58705</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59622</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.45381</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65504</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.82309</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.00054</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>-0.04198</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-0.04803</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8306399999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.04762</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.09923999999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.07490000000000001</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.10073</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.07185999999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.09312000000000001</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.06425</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.08231000000000001</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.06358</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.13942</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.07216</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.06520000000000001</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>-0.02518</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.06770999999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.07720999999999999</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.12844</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.12241</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.13439</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.11767</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35435</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9549500000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.06164</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.22799</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.09658</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.25138</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.10144</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25419</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27195</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.19319</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5967</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88518</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13538</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70345</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.23203</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.17275</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.22037</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.19024</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.03777</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>-0.008410000000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>-0.02995</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>-0.04316</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.13042</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.19585</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32475</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27298</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.25079</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14921</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14793</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15259</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.57256</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.60561</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14434</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14171</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14866</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14957</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14681</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13165</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11776</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11829</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17494</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4407799999999999</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54244</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.04141</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.03476</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23564</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25448</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.18292</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.25365</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.23787</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24909</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.18456</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.06949</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.16763</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24107</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.25359</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.23642</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47079</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70751</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29749</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34922</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5765</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65132</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83361</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34484</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25987</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13137</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.1943</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24305</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27832</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12663</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.22545</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.23665</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14225</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.19409</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.20453</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63548</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6022000000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59162</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45454</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6205900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45291</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47721</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48985</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56088</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.18982</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.19022</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.01559</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.08708</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.04254</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.23089</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.08948</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.03771</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.20622</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50622</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6032799999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7091499999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5319400000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8061</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74161</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59277</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6412599999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47988</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47284</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49812</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45841</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.22254</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.23868</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15302</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.19279</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.06423999999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.23536</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41927</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.47565</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.50164</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47645</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.01449</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.19009</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36408</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.13192</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23141</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24604</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.0244</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.22434</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.02376</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25504</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.03642</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14218</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15117</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.004900000000000001</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21553</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22626</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13872</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21034</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26479</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25777</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35196</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22761</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21709</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18062</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01445</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00327</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04072</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03412</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21498</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26755</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24243</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24492</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24469</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25033</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27253</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26901</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27741</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26812</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27416</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26707</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2524</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19091</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05727</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06662</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22732</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22465</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14855</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26968</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24598</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20679</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1902</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21504</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22586</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17037</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19025</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2228</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22253</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24398</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23222</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21543</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22701</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24703</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18435</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06631999999999999</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49731</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50145</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.50417</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.18232</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19632</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09831999999999999</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00621</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20754</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03156</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.00297</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07428</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02641</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.02299</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05233</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.19074</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.20561</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.22823</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.25637</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.26119</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.25822</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.26359</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32496</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08733</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.00508</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.01518</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-0.00736</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>-0.04764</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.23485</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.26315</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.27337</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.09977</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.21322</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.13795</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.01493</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33078</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.005860000000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.42679</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.24082</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.20921</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.23551</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.22323</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.20375</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.20525</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.20485</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.24187</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.17203</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.25518</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.22439</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.24652</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.39527</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42478</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70543</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36876</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44252</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.09265000000000001</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.02835</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>-0.02377</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>-0.01591</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.08979999999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.27633</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.15185</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.18389</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.02043</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.07238</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.26111</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.26447</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.52235</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45755</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5477799999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.44188</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.49591</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47729</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7081799999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74688</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.51573</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44102</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37525</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25894</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25805</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20533</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23116</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01471</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02517</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24074</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.01853</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03418</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00827</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>-0.00107</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.11965</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11098</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.20463</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18392</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.10638</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.23388</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.26395</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37617</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.76164</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.23575</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.21391</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.20505</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.17298</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.17301</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.17806</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.23208</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.02005</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.03158</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.03028</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07987000000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.01038</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.02793</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.0319</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.03924</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.02206</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.03811999999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.02819</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13412</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.01359</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.14091</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.16103</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.2046</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.009380000000000001</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.01672</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.02053</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.46484</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53547</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.39077</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.49819</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22335</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.20373</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.13571</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22302</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.20998</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13233</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14096</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.11464</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03162</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03343</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.03478</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.03813</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.03107</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.01445</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03772</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.02461</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.03323</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.08953</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04179</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.0419</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.03264</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.04661</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.0325</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02337</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.03729</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.03676</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.02627</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.18319</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21603</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23594</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23932</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24534</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.26692</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26861</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.384</v>
       </c>
     </row>
   </sheetData>
